--- a/artfynd/A 27698-2026 artfynd.xlsx
+++ b/artfynd/A 27698-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136025200</v>
       </c>
       <c r="B2" t="n">
-        <v>92296</v>
+        <v>92310</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136025183</v>
       </c>
       <c r="B3" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136025184</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136025185</v>
       </c>
       <c r="B5" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136025186</v>
       </c>
       <c r="B6" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136025188</v>
       </c>
       <c r="B7" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136025189</v>
       </c>
       <c r="B8" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136025190</v>
       </c>
       <c r="B9" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136025191</v>
       </c>
       <c r="B10" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136025192</v>
       </c>
       <c r="B11" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136025193</v>
       </c>
       <c r="B12" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136025194</v>
       </c>
       <c r="B13" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136025195</v>
       </c>
       <c r="B14" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136025196</v>
       </c>
       <c r="B15" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136025197</v>
       </c>
       <c r="B16" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136025198</v>
       </c>
       <c r="B17" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27698-2026 artfynd.xlsx
+++ b/artfynd/A 27698-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136025200</v>
       </c>
       <c r="B2" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136025183</v>
       </c>
       <c r="B3" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136025184</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136025185</v>
       </c>
       <c r="B5" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136025186</v>
       </c>
       <c r="B6" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136025188</v>
       </c>
       <c r="B7" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136025189</v>
       </c>
       <c r="B8" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136025190</v>
       </c>
       <c r="B9" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136025191</v>
       </c>
       <c r="B10" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136025192</v>
       </c>
       <c r="B11" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136025193</v>
       </c>
       <c r="B12" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136025194</v>
       </c>
       <c r="B13" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136025195</v>
       </c>
       <c r="B14" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136025196</v>
       </c>
       <c r="B15" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136025197</v>
       </c>
       <c r="B16" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136025198</v>
       </c>
       <c r="B17" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27698-2026 artfynd.xlsx
+++ b/artfynd/A 27698-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136025200</v>
       </c>
       <c r="B2" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136025184</v>
       </c>
       <c r="B4" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136025185</v>
       </c>
       <c r="B5" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136025186</v>
       </c>
       <c r="B6" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136025188</v>
       </c>
       <c r="B7" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136025189</v>
       </c>
       <c r="B8" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136025190</v>
       </c>
       <c r="B9" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136025191</v>
       </c>
       <c r="B10" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136025192</v>
       </c>
       <c r="B11" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136025193</v>
       </c>
       <c r="B12" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136025194</v>
       </c>
       <c r="B13" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136025195</v>
       </c>
       <c r="B14" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136025196</v>
       </c>
       <c r="B15" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136025197</v>
       </c>
       <c r="B16" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136025198</v>
       </c>
       <c r="B17" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27698-2026 artfynd.xlsx
+++ b/artfynd/A 27698-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136025200</v>
       </c>
       <c r="B2" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136025183</v>
       </c>
       <c r="B3" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136025184</v>
       </c>
       <c r="B4" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136025185</v>
       </c>
       <c r="B5" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136025186</v>
       </c>
       <c r="B6" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136025188</v>
       </c>
       <c r="B7" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136025189</v>
       </c>
       <c r="B8" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136025190</v>
       </c>
       <c r="B9" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136025191</v>
       </c>
       <c r="B10" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136025192</v>
       </c>
       <c r="B11" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136025193</v>
       </c>
       <c r="B12" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136025194</v>
       </c>
       <c r="B13" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136025195</v>
       </c>
       <c r="B14" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136025196</v>
       </c>
       <c r="B15" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136025197</v>
       </c>
       <c r="B16" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136025198</v>
       </c>
       <c r="B17" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27698-2026 artfynd.xlsx
+++ b/artfynd/A 27698-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136025200</v>
       </c>
       <c r="B2" t="n">
-        <v>92313</v>
+        <v>92319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136025183</v>
       </c>
       <c r="B3" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136025184</v>
       </c>
       <c r="B4" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136025185</v>
       </c>
       <c r="B5" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136025186</v>
       </c>
       <c r="B6" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136025188</v>
       </c>
       <c r="B7" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136025189</v>
       </c>
       <c r="B8" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136025190</v>
       </c>
       <c r="B9" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136025191</v>
       </c>
       <c r="B10" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136025192</v>
       </c>
       <c r="B11" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136025193</v>
       </c>
       <c r="B12" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136025194</v>
       </c>
       <c r="B13" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136025195</v>
       </c>
       <c r="B14" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136025196</v>
       </c>
       <c r="B15" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136025197</v>
       </c>
       <c r="B16" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136025198</v>
       </c>
       <c r="B17" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27698-2026 artfynd.xlsx
+++ b/artfynd/A 27698-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136025200</v>
       </c>
       <c r="B2" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136025183</v>
       </c>
       <c r="B3" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136025184</v>
       </c>
       <c r="B4" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136025185</v>
       </c>
       <c r="B5" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136025186</v>
       </c>
       <c r="B6" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136025188</v>
       </c>
       <c r="B7" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136025189</v>
       </c>
       <c r="B8" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136025190</v>
       </c>
       <c r="B9" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136025191</v>
       </c>
       <c r="B10" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136025192</v>
       </c>
       <c r="B11" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136025193</v>
       </c>
       <c r="B12" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136025194</v>
       </c>
       <c r="B13" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136025195</v>
       </c>
       <c r="B14" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136025196</v>
       </c>
       <c r="B15" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136025197</v>
       </c>
       <c r="B16" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136025198</v>
       </c>
       <c r="B17" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27698-2026 artfynd.xlsx
+++ b/artfynd/A 27698-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136025200</v>
       </c>
       <c r="B2" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136025183</v>
       </c>
       <c r="B3" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136025184</v>
       </c>
       <c r="B4" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136025185</v>
       </c>
       <c r="B5" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136025186</v>
       </c>
       <c r="B6" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136025188</v>
       </c>
       <c r="B7" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136025189</v>
       </c>
       <c r="B8" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136025190</v>
       </c>
       <c r="B9" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136025191</v>
       </c>
       <c r="B10" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136025192</v>
       </c>
       <c r="B11" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136025193</v>
       </c>
       <c r="B12" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136025194</v>
       </c>
       <c r="B13" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136025195</v>
       </c>
       <c r="B14" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136025196</v>
       </c>
       <c r="B15" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136025197</v>
       </c>
       <c r="B16" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136025198</v>
       </c>
       <c r="B17" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27698-2026 artfynd.xlsx
+++ b/artfynd/A 27698-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136025200</v>
       </c>
       <c r="B2" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136025183</v>
       </c>
       <c r="B3" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136025184</v>
       </c>
       <c r="B4" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136025185</v>
       </c>
       <c r="B5" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136025186</v>
       </c>
       <c r="B6" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136025188</v>
       </c>
       <c r="B7" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136025189</v>
       </c>
       <c r="B8" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136025190</v>
       </c>
       <c r="B9" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136025191</v>
       </c>
       <c r="B10" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136025192</v>
       </c>
       <c r="B11" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136025193</v>
       </c>
       <c r="B12" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136025194</v>
       </c>
       <c r="B13" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136025195</v>
       </c>
       <c r="B14" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136025196</v>
       </c>
       <c r="B15" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136025197</v>
       </c>
       <c r="B16" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136025198</v>
       </c>
       <c r="B17" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27698-2026 artfynd.xlsx
+++ b/artfynd/A 27698-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136025200</v>
       </c>
       <c r="B2" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136025184</v>
       </c>
       <c r="B4" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136025185</v>
       </c>
       <c r="B5" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136025186</v>
       </c>
       <c r="B6" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136025188</v>
       </c>
       <c r="B7" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136025189</v>
       </c>
       <c r="B8" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136025190</v>
       </c>
       <c r="B9" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136025191</v>
       </c>
       <c r="B10" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136025192</v>
       </c>
       <c r="B11" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136025193</v>
       </c>
       <c r="B12" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136025194</v>
       </c>
       <c r="B13" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136025195</v>
       </c>
       <c r="B14" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136025196</v>
       </c>
       <c r="B15" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136025197</v>
       </c>
       <c r="B16" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136025198</v>
       </c>
       <c r="B17" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27698-2026 artfynd.xlsx
+++ b/artfynd/A 27698-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136025200</v>
       </c>
       <c r="B2" t="n">
-        <v>92334</v>
+        <v>92347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136025183</v>
       </c>
       <c r="B3" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136025184</v>
       </c>
       <c r="B4" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136025185</v>
       </c>
       <c r="B5" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136025186</v>
       </c>
       <c r="B6" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136025188</v>
       </c>
       <c r="B7" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136025189</v>
       </c>
       <c r="B8" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136025190</v>
       </c>
       <c r="B9" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136025191</v>
       </c>
       <c r="B10" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136025192</v>
       </c>
       <c r="B11" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136025193</v>
       </c>
       <c r="B12" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136025194</v>
       </c>
       <c r="B13" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136025195</v>
       </c>
       <c r="B14" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136025196</v>
       </c>
       <c r="B15" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136025197</v>
       </c>
       <c r="B16" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136025198</v>
       </c>
       <c r="B17" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27698-2026 artfynd.xlsx
+++ b/artfynd/A 27698-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136025200</v>
       </c>
       <c r="B2" t="n">
-        <v>92347</v>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136025183</v>
       </c>
       <c r="B3" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136025184</v>
       </c>
       <c r="B4" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136025185</v>
       </c>
       <c r="B5" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136025186</v>
       </c>
       <c r="B6" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136025188</v>
       </c>
       <c r="B7" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136025189</v>
       </c>
       <c r="B8" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136025190</v>
       </c>
       <c r="B9" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136025191</v>
       </c>
       <c r="B10" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136025192</v>
       </c>
       <c r="B11" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136025193</v>
       </c>
       <c r="B12" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136025194</v>
       </c>
       <c r="B13" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136025195</v>
       </c>
       <c r="B14" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136025196</v>
       </c>
       <c r="B15" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136025197</v>
       </c>
       <c r="B16" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136025198</v>
       </c>
       <c r="B17" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
